--- a/Arquivos_TFO/dados_acareacoes_TFO.xlsx
+++ b/Arquivos_TFO/dados_acareacoes_TFO.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -554,194 +554,6 @@
       <c r="I3" t="inlineStr">
         <is>
           <t>2026-06-08 12:10:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>3320041492030</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>(TFO LOC) AILTON PASSOS</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Fake Delivery</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Lorrayne Figueiredo</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>+5533991293996</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Rua Doutor Nuno Cunha Melo 120, Teófilo Otoni</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Kit 2 Conjunto Espera Marido PLUS SIZE cropped + calcinha calesson sem bojo e renda*1</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>19.49</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2026-06-05 13:07:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>3320075481967</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>(TFO LOC) WEBERTON GONÇALVES</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Fake Delivery</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>jaiane</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>+5533988777117</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Rua Minervino de Castro Pinto 222 Apartamento 301, Teófilo Otoni</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Bota Lóris Shoes Feminina Cano Alto Salto Baixo Bloco Conforto Elegante Montaria 831*1</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2026-06-05 12:49:12</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>3320009492940</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>(TFO INT) LUCAS DE SÁ (NANUQUE)</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Fake Delivery</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Mary Petsolt</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>+5533997062360</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Avenida rio São Francisco 101 Casa, Serra dos Aimorés</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Kit 30 Peças: Kit 4 Cadernos pequeno de Caligrafia + 6 Canetas + 20 Recargas, Treino de Escrita Infantil Pré-Escolar, Aprendizagem Divertida Reutilizável*1</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>3.8</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2026-06-05 12:47:50</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>3320004494248</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>(TFO INT) LUCAS DE SÁ (NANUQUE)</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Fake Delivery</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Mary Petsolt</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>+5533997062360</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Avenida rio São Francisco 101 Casa, Serra dos Aimorés</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Polygel XD LED UV Profissional 15g F1 Alongamento Poly Gel Unhas de Gel*2</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0.89</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2026-06-05 12:47:33</t>
         </is>
       </c>
     </row>
